--- a/data/Administrator.xlsx
+++ b/data/Administrator.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <s:workbookPr codeName="ThisWorkbook"/>
-  <s:bookViews>
-    <s:workbookView activeTab="1"/>
-  </s:bookViews>
-  <s:sheets>
-    <s:sheet name="login" sheetId="1" r:id="rId1"/>
-    <s:sheet name="getDataList" sheetId="2" r:id="rId2"/>
-  </s:sheets>
-  <s:definedNames/>
-  <s:calcPr calcId="124519" fullCalcOnLoad="1"/>
-</s:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Romens_Api_Test\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D96F788-0DC2-4708-814F-F9EBF7980134}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="login" sheetId="1" r:id="rId1"/>
+    <sheet name="getDataList" sheetId="2" r:id="rId2"/>
+    <sheet name="importData" sheetId="3" r:id="rId3"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
   <si>
     <t>case_id</t>
   </si>
@@ -75,33 +82,44 @@
   </si>
   <si>
     <t>{'draw': 0}</t>
+  </si>
+  <si>
+    <t>importData</t>
+  </si>
+  <si>
+    <t>/admin/ShopManage/importData</t>
+  </si>
+  <si>
+    <t>{"CODE":true}</t>
+  </si>
+  <si>
+    <t>导入门店-导入成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -132,22 +150,30 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" borderId="0" fillId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" builtinId="0" xfId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -413,24 +439,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="8.5" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="18.375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.5" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="48.125" customWidth="1" min="6" max="6"/>
-    <col width="14.75" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48.125" customWidth="1"/>
+    <col min="7" max="7" width="14.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" customFormat="1" s="2">
+    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -456,8 +478,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" customFormat="1" s="2">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -483,29 +505,26 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="10.875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="101.25" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="43.125" customWidth="1" min="6" max="6"/>
-    <col width="9.25" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="101.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.125" customWidth="1"/>
+    <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -531,8 +550,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -558,7 +577,78 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44D74AD1-C5EC-42D6-9333-71F456EFBB9A}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/Administrator.xlsx
+++ b/data/Administrator.xlsx
@@ -1,28 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Romens_Api_Test\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D96F788-0DC2-4708-814F-F9EBF7980134}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="login" sheetId="1" r:id="rId1"/>
-    <sheet name="getDataList" sheetId="2" r:id="rId2"/>
-    <sheet name="importData" sheetId="3" r:id="rId3"/>
-  </sheets>
-  <calcPr calcId="0"/>
-</workbook>
+<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <s:workbookPr codeName="ThisWorkbook"/>
+  <s:bookViews>
+    <s:workbookView activeTab="11"/>
+  </s:bookViews>
+  <s:sheets>
+    <s:sheet name="login" sheetId="1" r:id="rId1"/>
+    <s:sheet name="getDataList" sheetId="2" r:id="rId2"/>
+    <s:sheet name="importData" sheetId="3" r:id="rId3"/>
+    <s:sheet name="getDataListByChild" sheetId="4" r:id="rId4"/>
+    <s:sheet name="getDoctorInfo" sheetId="5" r:id="rId5"/>
+    <s:sheet name="getlist" sheetId="6" r:id="rId6"/>
+    <s:sheet name="getData" sheetId="7" r:id="rId7"/>
+    <s:sheet name="getShopOrder" sheetId="8" r:id="rId8"/>
+    <s:sheet name="getDoctorOrder" sheetId="9" r:id="rId9"/>
+    <s:sheet name="getPharmacistOrder" sheetId="10" r:id="rId10"/>
+    <s:sheet name="getAppointment" sheetId="11" r:id="rId11"/>
+    <s:sheet name="getGoodsList" sheetId="12" r:id="rId12"/>
+  </s:sheets>
+  <s:definedNames/>
+  <s:calcPr calcId="124519" fullCalcOnLoad="1"/>
+</s:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="51">
   <si>
     <t>case_id</t>
   </si>
@@ -87,39 +90,121 @@
     <t>importData</t>
   </si>
   <si>
+    <t>导入门店-导入成功</t>
+  </si>
+  <si>
     <t>/admin/ShopManage/importData</t>
   </si>
   <si>
-    <t>{"CODE":true}</t>
-  </si>
-  <si>
-    <t>导入门店-导入成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>{"status_code":200}</t>
+  </si>
+  <si>
+    <t>getDataListByChild</t>
+  </si>
+  <si>
+    <t>子账号获取-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/ShopManage/getDataListByChild?shopId=&amp;shopName=&amp;phone=15589856997</t>
+  </si>
+  <si>
+    <t>{"draw":0}</t>
+  </si>
+  <si>
+    <t>getDoctorInfo</t>
+  </si>
+  <si>
+    <t>获取医师列表-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/Doctor/getDoctorInfo</t>
+  </si>
+  <si>
+    <t>获取药师列表-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/PharManage/getDataList?name=&amp;phone=&amp;state=0</t>
+  </si>
+  <si>
+    <t>getData</t>
+  </si>
+  <si>
+    <t>获取处方单列表-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/InquiryOrder/getDataList?start=2020-05-07&amp;end=2020-05-07&amp;shop=&amp;doctor=&amp;type=1&amp;ordercode=&amp;pharstate=</t>
+  </si>
+  <si>
+    <t>{"draw":'1'}</t>
+  </si>
+  <si>
+    <t>getShopOrder</t>
+  </si>
+  <si>
+    <t>获取门店开方量列表-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/AuditStatistics/getShopOrder</t>
+  </si>
+  <si>
+    <t>{"CODE":'1'}</t>
+  </si>
+  <si>
+    <t>getDoctorOrder</t>
+  </si>
+  <si>
+    <t>获取医生开方量列表-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/AuditStatistics/getDoctorOrder</t>
+  </si>
+  <si>
+    <t>getPharmacistOrder</t>
+  </si>
+  <si>
+    <t>获取药师开方量列表-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/AuditStatistics/getPharmacistOrder</t>
+  </si>
+  <si>
+    <t>获取预约列表数据-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/Appointment/getDataList</t>
+  </si>
+  <si>
+    <t>获取商品列表数据-获取成功</t>
+  </si>
+  <si>
+    <t>/admin/GoodsList/getDataList?goodsName=</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -150,30 +235,22 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" borderId="0" fillId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" builtinId="0" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -439,20 +516,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="48.125" customWidth="1"/>
-    <col min="7" max="7" width="14.75" bestFit="1" customWidth="1"/>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="18.375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="11.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="48.125" customWidth="1" min="6" max="6"/>
+    <col width="14.75" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" customFormat="1" s="2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -478,8 +559,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
+    <row r="2" spans="1:8" customFormat="1" s="2">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -505,26 +586,27 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="101.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43.125" customWidth="1"/>
-    <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
+    <col width="18.75" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="28.75" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="39.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="10.625" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -550,8 +632,225 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="18.75" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="31.125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="10.625" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="18.75" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="26.625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="41.625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="9.25" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="101.25" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="43.125" customWidth="1" min="6" max="6"/>
+    <col width="9.25" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -577,26 +876,29 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44D74AD1-C5EC-42D6-9333-71F456EFBB9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.375" bestFit="1" customWidth="1"/>
+    <col width="11" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="20.375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="31.375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="5.25" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="17.5" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,33 +924,466 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="17.375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="20.375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="80.125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="5.25" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="10" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13.375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="20.375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="27.75" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="9.25" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="55.25" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="9.25" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="104.875" customWidth="1" min="5" max="5"/>
+    <col width="9.25" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="13.625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="28.75" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="31.75" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
+  <cols>
+    <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="15.125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="28.75" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="34.375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="10.625" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>